--- a/hanmi/dist/20261025_韓美半導體模型_v0.2.xlsx
+++ b/hanmi/dist/20261025_韓美半導體模型_v0.2.xlsx
@@ -3479,7 +3479,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4072,7 +4072,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4527,7 +4527,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7825,7 +7825,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8034,7 +8034,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8137,7 +8137,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8240,7 +8240,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8343,7 +8343,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8436,7 +8436,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8529,7 +8529,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8622,7 +8622,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8715,7 +8715,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8808,7 +8808,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8901,7 +8901,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8994,7 +8994,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9087,7 +9087,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9180,7 +9180,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9273,7 +9273,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
